--- a/Test_Cases.xlsx
+++ b/Test_Cases.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6200" activeTab="2"/>
+    <workbookView windowWidth="19200" windowHeight="6200"/>
   </bookViews>
   <sheets>
     <sheet name="Login Module" sheetId="2" r:id="rId1"/>
